--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487077_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487077_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.3675</v>
+        <v>9.773999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>9.0007</v>
+        <v>9.460699999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3668</v>
+        <v>0.3133</v>
       </c>
       <c r="G2" t="n">
         <v>7.5395</v>
@@ -610,13 +610,13 @@
         <v>2.5091</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2419</v>
+        <v>0.1646</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3873</v>
+        <v>0.0727</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1454</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="V2" t="n">
         <v>2.4559</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>9.1914</v>
+        <v>8.1365</v>
       </c>
       <c r="E3" t="n">
-        <v>9.5205</v>
+        <v>8.2782</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3291</v>
+        <v>-0.1417</v>
       </c>
       <c r="G3" t="n">
         <v>6.8957</v>
@@ -688,13 +688,13 @@
         <v>2.7021</v>
       </c>
       <c r="S3" t="n">
-        <v>1.7867</v>
+        <v>0.7317</v>
       </c>
       <c r="T3" t="n">
-        <v>2.3426</v>
+        <v>1.1002</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5558999999999999</v>
+        <v>-0.3685</v>
       </c>
       <c r="V3" t="n">
         <v>-1.228</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.6839</v>
+        <v>5.5232</v>
       </c>
       <c r="E4" t="n">
-        <v>4.1724</v>
+        <v>3.9314</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5115</v>
+        <v>1.5918</v>
       </c>
       <c r="G4" t="n">
         <v>5.9005</v>
@@ -766,13 +766,13 @@
         <v>2.7021</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6326000000000001</v>
+        <v>0.4719</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9624</v>
+        <v>0.7215</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3299</v>
+        <v>-0.2496</v>
       </c>
       <c r="V4" t="n">
         <v>-0.6562</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.0065</v>
+        <v>4.1136</v>
       </c>
       <c r="E5" t="n">
         <v>5.4595</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.4529</v>
+        <v>-1.3459</v>
       </c>
       <c r="G5" t="n">
         <v>3.1411</v>
@@ -844,13 +844,13 @@
         <v>2.1231</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2697</v>
+        <v>-0.1626</v>
       </c>
       <c r="T5" t="n">
         <v>0.2657</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5354</v>
+        <v>-0.4283</v>
       </c>
       <c r="V5" t="n">
         <v>0.9421</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.6816</v>
+        <v>2.755</v>
       </c>
       <c r="E6" t="n">
-        <v>1.193</v>
+        <v>1.0522</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4886</v>
+        <v>1.7028</v>
       </c>
       <c r="G6" t="n">
         <v>1.0888</v>
@@ -922,13 +922,13 @@
         <v>1.9301</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3649</v>
+        <v>0.4382</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3993</v>
+        <v>0.2585</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0344</v>
+        <v>0.1798</v>
       </c>
       <c r="V6" t="n">
         <v>1.228</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.7262</v>
+        <v>1.5587</v>
       </c>
       <c r="E7" t="n">
-        <v>1.0424</v>
+        <v>1.1425</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6839</v>
+        <v>0.4162</v>
       </c>
       <c r="G7" t="n">
         <v>1.1036</v>
@@ -1000,13 +1000,13 @@
         <v>0.965</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5803</v>
+        <v>0.4128</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1639</v>
+        <v>-0.0638</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7442</v>
+        <v>0.4766</v>
       </c>
       <c r="V7" t="n">
         <v>0.0422</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. REY GUTIERREZ</t>
+          <t>A. REYES ABAD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0049</v>
+        <v>0.5916</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6316000000000001</v>
+        <v>-0.7439</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6366000000000001</v>
+        <v>1.3355</v>
       </c>
       <c r="G8" t="n">
-        <v>1.2148</v>
+        <v>-0.2273</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0052</v>
+        <v>0.0612</v>
       </c>
       <c r="I8" t="n">
-        <v>1.2096</v>
+        <v>-0.2885</v>
       </c>
       <c r="J8" t="n">
-        <v>1.0481</v>
+        <v>0.7536</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3726</v>
+        <v>0.6157</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6755</v>
+        <v>0.1378</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1667</v>
+        <v>-0.9808</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3674</v>
+        <v>-0.5546</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5341</v>
+        <v>-0.4263</v>
       </c>
       <c r="P8" t="n">
-        <v>0.965</v>
+        <v>0.772</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.9301</v>
       </c>
       <c r="R8" t="n">
-        <v>0.965</v>
+        <v>2.7021</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6709000000000001</v>
+        <v>0.0046</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4164</v>
+        <v>0.4326</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2545</v>
+        <v>-0.428</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.5138</v>
+        <v>0.0422</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.5138</v>
+        <v>0.0422</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. REYES ABAD</t>
+          <t>A. REY GUTIERREZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1421</v>
+        <v>0.2687</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5043</v>
+        <v>0.9321</v>
       </c>
       <c r="F9" t="n">
-        <v>1.3623</v>
+        <v>-0.6633</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2273</v>
+        <v>1.2148</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0612</v>
+        <v>0.0052</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2885</v>
+        <v>1.2096</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7536</v>
+        <v>1.0481</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6157</v>
+        <v>0.3726</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1378</v>
+        <v>0.6755</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9808</v>
+        <v>0.1667</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5546</v>
+        <v>-0.3674</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4263</v>
+        <v>0.5341</v>
       </c>
       <c r="P9" t="n">
-        <v>0.772</v>
+        <v>0.965</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.7021</v>
+        <v>0.965</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7291</v>
+        <v>-0.3973</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3278</v>
+        <v>-0.116</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4013</v>
+        <v>-0.2813</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0422</v>
+        <v>-1.5138</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0422</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7056</v>
+        <v>-0.5787</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0177</v>
+        <v>0.1178</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7233000000000001</v>
+        <v>-0.6965</v>
       </c>
       <c r="G10" t="n">
         <v>-0.2791</v>
@@ -1234,13 +1234,13 @@
         <v>0.965</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1223</v>
+        <v>0.2492</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2234</v>
+        <v>-0.1233</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3457</v>
+        <v>0.3725</v>
       </c>
       <c r="V10" t="n">
         <v>-1.5138</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.6036</v>
+        <v>-2.6443</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.2953</v>
+        <v>-3.095</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6917</v>
+        <v>0.4507</v>
       </c>
       <c r="G11" t="n">
         <v>0.4204</v>
@@ -1312,13 +1312,13 @@
         <v>2.7021</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0641</v>
+        <v>0.0235</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4614</v>
+        <v>-0.2611</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5255</v>
+        <v>0.2845</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>29.2009</v>
+        <v>29.4983</v>
       </c>
       <c r="E12" t="n">
-        <v>26.2382</v>
+        <v>26.5355</v>
       </c>
       <c r="F12" t="n">
         <v>2.9629</v>
@@ -1390,13 +1390,13 @@
         <v>20.2657</v>
       </c>
       <c r="S12" t="n">
-        <v>1.6393</v>
+        <v>1.9366</v>
       </c>
       <c r="T12" t="n">
-        <v>1.9898</v>
+        <v>2.287</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3505999999999998</v>
+        <v>-0.3504999999999998</v>
       </c>
       <c r="V12" t="n">
         <v>-0.2013999999999998</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>I. VICUÑA ROYO</t>
+          <t>M. ARIZTIMUÑO MORRAS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5832000000000001</v>
+        <v>0.003</v>
       </c>
       <c r="E13" t="n">
-        <v>3.074</v>
+        <v>3.6414</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.4907</v>
+        <v>-3.6383</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.0367</v>
+        <v>-2.0109</v>
       </c>
       <c r="H13" t="n">
-        <v>1.7437</v>
+        <v>-2.218</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.7804</v>
+        <v>0.2071</v>
       </c>
       <c r="J13" t="n">
-        <v>3.5482</v>
+        <v>3.6549</v>
       </c>
       <c r="K13" t="n">
-        <v>4.1344</v>
+        <v>0.4397</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.5862000000000001</v>
+        <v>3.2152</v>
       </c>
       <c r="M13" t="n">
-        <v>-4.5848</v>
+        <v>-5.6659</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.3906</v>
+        <v>-2.6577</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.1942</v>
+        <v>-3.0082</v>
       </c>
       <c r="P13" t="n">
-        <v>-0</v>
+        <v>-1.158</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.9301</v>
+        <v>-3.8602</v>
       </c>
       <c r="R13" t="n">
-        <v>1.9301</v>
+        <v>2.7021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9234</v>
+        <v>0.0618</v>
       </c>
       <c r="T13" t="n">
-        <v>1.17</v>
+        <v>0.4908</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2466</v>
+        <v>-0.429</v>
       </c>
       <c r="V13" t="n">
-        <v>0.6965</v>
+        <v>3.1102</v>
       </c>
       <c r="W13" t="n">
-        <v>0.2859</v>
+        <v>3.3558</v>
       </c>
       <c r="X13" t="n">
-        <v>0.4106</v>
+        <v>-0.2456</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. MENDIVIL ODERIZ</t>
+          <t>K. ABU SHAMS SANCHEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3313</v>
+        <v>-0.1277</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.2358</v>
+        <v>2.3288</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5671</v>
+        <v>-2.4566</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.1283</v>
+        <v>0.8081</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.2439</v>
+        <v>-1.0184</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1157</v>
+        <v>1.8265</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0543</v>
+        <v>2.5638</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.6212</v>
+        <v>0.7245</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6755</v>
+        <v>1.8393</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.1825</v>
+        <v>-1.7557</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.6227</v>
+        <v>-1.7428</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.5598</v>
+        <v>-0.0129</v>
       </c>
       <c r="P14" t="n">
-        <v>-0</v>
+        <v>1.158</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.9301</v>
+        <v>1.158</v>
       </c>
       <c r="S14" t="n">
-        <v>1.9301</v>
+        <v>-0.6203</v>
       </c>
       <c r="T14" t="n">
-        <v>1.1105</v>
+        <v>-0.235</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8196</v>
+        <v>-0.3854</v>
       </c>
       <c r="V14" t="n">
-        <v>0.5295</v>
+        <v>-1.4736</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5295</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-1.4736</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. ARIZTIMUÑO MORRAS</t>
+          <t>I. VICUÑA ROYO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.4316</v>
+        <v>-0.2919</v>
       </c>
       <c r="E15" t="n">
-        <v>3.7415</v>
+        <v>2.1727</v>
       </c>
       <c r="F15" t="n">
-        <v>-4.1731</v>
+        <v>-2.4646</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.0109</v>
+        <v>-1.0367</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.218</v>
+        <v>1.7437</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2071</v>
+        <v>-2.7804</v>
       </c>
       <c r="J15" t="n">
-        <v>3.6549</v>
+        <v>3.5482</v>
       </c>
       <c r="K15" t="n">
-        <v>0.4397</v>
+        <v>4.1344</v>
       </c>
       <c r="L15" t="n">
-        <v>3.2152</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>-5.6659</v>
+        <v>-4.5848</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.6577</v>
+        <v>-2.3906</v>
       </c>
       <c r="O15" t="n">
-        <v>-3.0082</v>
+        <v>-2.1942</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.158</v>
+        <v>-0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.8602</v>
+        <v>-1.9301</v>
       </c>
       <c r="R15" t="n">
-        <v>2.7021</v>
+        <v>1.9301</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3728</v>
+        <v>0.0483</v>
       </c>
       <c r="T15" t="n">
-        <v>0.591</v>
+        <v>0.2687</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.9637</v>
+        <v>-0.2205</v>
       </c>
       <c r="V15" t="n">
-        <v>3.1102</v>
+        <v>0.6965</v>
       </c>
       <c r="W15" t="n">
-        <v>3.3558</v>
+        <v>0.2859</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2456</v>
+        <v>0.4106</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>K. ABU SHAMS SANCHEZ</t>
+          <t>J. MENDIVIL ODERIZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.7487</v>
+        <v>-0.7715</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0284</v>
+        <v>-0.9368</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.7771</v>
+        <v>0.1653</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8081</v>
+        <v>-2.1283</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.0184</v>
+        <v>-2.2439</v>
       </c>
       <c r="I16" t="n">
-        <v>1.8265</v>
+        <v>0.1157</v>
       </c>
       <c r="J16" t="n">
-        <v>2.5638</v>
+        <v>0.0543</v>
       </c>
       <c r="K16" t="n">
-        <v>0.7245</v>
+        <v>-0.6212</v>
       </c>
       <c r="L16" t="n">
-        <v>1.8393</v>
+        <v>0.6755</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.7557</v>
+        <v>-2.1825</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.7428</v>
+        <v>-1.6227</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0129</v>
+        <v>-0.5598</v>
       </c>
       <c r="P16" t="n">
-        <v>1.158</v>
+        <v>-0</v>
       </c>
       <c r="Q16" t="n">
+        <v>-1.9301</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.9301</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.8272</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.4095</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.4177</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.5295</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.5295</v>
+      </c>
+      <c r="X16" t="n">
         <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.158</v>
-      </c>
-      <c r="S16" t="n">
-        <v>-1.2413</v>
-      </c>
-      <c r="T16" t="n">
-        <v>-0.5354</v>
-      </c>
-      <c r="U16" t="n">
-        <v>-0.7059</v>
-      </c>
-      <c r="V16" t="n">
-        <v>-1.4736</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>-1.4736</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.9162</v>
+        <v>-1.8898</v>
       </c>
       <c r="E17" t="n">
         <v>-1.8136</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1027</v>
+        <v>-0.0762</v>
       </c>
       <c r="G17" t="n">
         <v>-4.864</v>
@@ -1780,13 +1780,13 @@
         <v>1.9301</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4918</v>
+        <v>0.5182</v>
       </c>
       <c r="T17" t="n">
         <v>0.1018</v>
       </c>
       <c r="U17" t="n">
-        <v>0.39</v>
+        <v>0.4164</v>
       </c>
       <c r="V17" t="n">
         <v>2.4559</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.9394</v>
+        <v>-1.9129</v>
       </c>
       <c r="E18" t="n">
         <v>1.0456</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.985</v>
+        <v>-2.9585</v>
       </c>
       <c r="G18" t="n">
         <v>-1.5967</v>
@@ -1858,13 +1858,13 @@
         <v>1.9301</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0568</v>
+        <v>-0.0304</v>
       </c>
       <c r="T18" t="n">
         <v>0.2208</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2776</v>
+        <v>-0.2512</v>
       </c>
       <c r="V18" t="n">
         <v>-0.2859</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.4552</v>
+        <v>-2.4152</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.596</v>
+        <v>-0.7963</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.8592</v>
+        <v>-1.6189</v>
       </c>
       <c r="G19" t="n">
         <v>-2.7039</v>
@@ -1936,13 +1936,13 @@
         <v>1.3511</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0853</v>
+        <v>0.1253</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2803</v>
+        <v>0.08</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.195</v>
+        <v>0.0453</v>
       </c>
       <c r="V19" t="n">
         <v>-1.1877</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.4225</v>
+        <v>-3.9013</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.8128</v>
+        <v>-1.6125</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.6097</v>
+        <v>-2.2888</v>
       </c>
       <c r="G20" t="n">
         <v>-0.1893</v>
@@ -2014,13 +2014,13 @@
         <v>1.5441</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9749</v>
+        <v>-0.4538</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8328</v>
+        <v>-0.6325</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1421</v>
+        <v>0.1788</v>
       </c>
       <c r="V20" t="n">
         <v>-0.9421</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.5523</v>
+        <v>-4.7439</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.8593</v>
+        <v>-1.5588</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.693</v>
+        <v>-3.1851</v>
       </c>
       <c r="G21" t="n">
         <v>-5.0697</v>
@@ -2092,13 +2092,13 @@
         <v>1.5441</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1019</v>
+        <v>-0.2935</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5949</v>
+        <v>-0.2945</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.507</v>
+        <v>0.001</v>
       </c>
       <c r="V21" t="n">
         <v>0.0403</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>I. ECHEONDO LACALLE</t>
+          <t>H. OREJA ELSO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.3027</v>
+        <v>-5.1445</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.4176</v>
+        <v>-3.3161</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.8851</v>
+        <v>-1.8284</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.2693</v>
+        <v>-5.7374</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.7099</v>
+        <v>-1.2213</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.5594</v>
+        <v>-4.5162</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2263</v>
+        <v>-1.7403</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1449</v>
+        <v>0.1811</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0814</v>
+        <v>-1.9214</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.4956</v>
+        <v>-3.9971</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.8548</v>
+        <v>-1.4023</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.6408</v>
+        <v>-2.5948</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.772</v>
+        <v>0.193</v>
       </c>
       <c r="Q22" t="n">
         <v>-1.9301</v>
       </c>
       <c r="R22" t="n">
-        <v>1.158</v>
+        <v>2.1231</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5195</v>
+        <v>0.3999</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7139</v>
+        <v>0.3543</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1943</v>
+        <v>0.0456</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.7418</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.7418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>H. OREJA ELSO</t>
+          <t>I. ECHEONDO LACALLE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.3468</v>
+        <v>-6.0023</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.1172</v>
+        <v>-2.1172</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.2296</v>
+        <v>-3.8851</v>
       </c>
       <c r="G23" t="n">
-        <v>-5.7374</v>
+        <v>-2.2693</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.2213</v>
+        <v>-0.7099</v>
       </c>
       <c r="I23" t="n">
-        <v>-4.5162</v>
+        <v>-1.5594</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.7403</v>
+        <v>0.2263</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1811</v>
+        <v>0.1449</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.9214</v>
+        <v>0.0814</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.9971</v>
+        <v>-2.4956</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.4023</v>
+        <v>-0.8548</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.5948</v>
+        <v>-1.6408</v>
       </c>
       <c r="P23" t="n">
-        <v>0.193</v>
+        <v>-0.772</v>
       </c>
       <c r="Q23" t="n">
         <v>-1.9301</v>
       </c>
       <c r="R23" t="n">
-        <v>2.1231</v>
+        <v>1.158</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8024</v>
+        <v>-0.2191</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4468</v>
+        <v>-0.4134</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3556</v>
+        <v>0.1943</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-2.7418</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-2.7418</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-29.2009</v>
+        <v>-27.198</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.962800000000001</v>
+        <v>-2.9628</v>
       </c>
       <c r="F24" t="n">
-        <v>-26.2381</v>
+        <v>-24.2352</v>
       </c>
       <c r="G24" t="n">
         <v>-26.7981</v>
@@ -2308,7 +2308,7 @@
         <v>4.2308</v>
       </c>
       <c r="M24" t="n">
-        <v>-35.0379</v>
+        <v>-35.03790000000001</v>
       </c>
       <c r="N24" t="n">
         <v>-19.265</v>
@@ -2326,13 +2326,13 @@
         <v>19.3009</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.639</v>
+        <v>0.3636</v>
       </c>
       <c r="T24" t="n">
-        <v>0.3506000000000004</v>
+        <v>0.3505</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.9896</v>
+        <v>0.01300000000000001</v>
       </c>
       <c r="V24" t="n">
         <v>0.2013000000000003</v>
